--- a/public/static/销售订单导入模板.xlsx
+++ b/public/static/销售订单导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="销售订单" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>序号</t>
   </si>
   <si>
-    <t>客户物料号(必填)</t>
+    <t>客户货号\规格型号(必填)</t>
   </si>
   <si>
     <t>数量(必填)</t>
@@ -41,7 +41,31 @@
     <t>交货日期(必填)</t>
   </si>
   <si>
-    <t>要求</t>
+    <t>单价</t>
+  </si>
+  <si>
+    <t>税率(%)</t>
+  </si>
+  <si>
+    <t>打字内容</t>
+  </si>
+  <si>
+    <t>精度等级</t>
+  </si>
+  <si>
+    <t>振动等级</t>
+  </si>
+  <si>
+    <t>油脂</t>
+  </si>
+  <si>
+    <t>油脂量</t>
+  </si>
+  <si>
+    <t>游隙</t>
+  </si>
+  <si>
+    <t>包装方式</t>
   </si>
 </sst>
 </file>
@@ -1060,15 +1084,23 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1" outlineLevelCol="4"/>
+  <dimension ref="A1:M123"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="20" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20" style="3" customWidth="1"/>
-    <col min="3" max="5" width="20" style="2" customWidth="1"/>
+    <col min="1" max="1" width="7.63636363636364" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.1818181818182" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.1818181818182" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.0909090909091" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.8181818181818" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.5454545454545" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10" style="2" customWidth="1"/>
+    <col min="10" max="12" width="11.6363636363636" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12.0909090909091" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:13">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1084,13 +1116,45 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:5">
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:13">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
     </row>
     <row r="3" customFormat="1" customHeight="1"/>
     <row r="4" customHeight="1" spans="2:2">

--- a/public/static/销售订单导入模板.xlsx
+++ b/public/static/销售订单导入模板.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="销售订单" sheetId="1" r:id="rId1"/>
+    <sheet name="说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,12 +28,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>序号</t>
   </si>
   <si>
-    <t>客户货号\规格型号(必填)</t>
+    <t>客户料号</t>
+  </si>
+  <si>
+    <t>品名规格</t>
   </si>
   <si>
     <t>数量(必填)</t>
@@ -41,7 +45,7 @@
     <t>交货日期(必填)</t>
   </si>
   <si>
-    <t>单价</t>
+    <t>单价(含税)</t>
   </si>
   <si>
     <t>税率(%)</t>
@@ -66,6 +70,9 @@
   </si>
   <si>
     <t>包装方式</t>
+  </si>
+  <si>
+    <t>1、客户货号和规格型号必须填写一项</t>
   </si>
 </sst>
 </file>
@@ -1084,23 +1091,24 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:N123"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.63636363636364" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.1818181818182" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.1818181818182" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.0909090909091" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.8181818181818" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10.5454545454545" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10" style="2" customWidth="1"/>
-    <col min="10" max="12" width="11.6363636363636" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12.0909090909091" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.5454545454545" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.4545454545455" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.1818181818182" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.0909090909091" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.8181818181818" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.5454545454545" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10" style="2" customWidth="1"/>
+    <col min="11" max="13" width="11.6363636363636" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12.0909090909091" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:14">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1140,8 +1148,11 @@
       <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:13">
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:14">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1155,371 +1166,512 @@
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
     </row>
     <row r="3" customFormat="1" customHeight="1"/>
-    <row r="4" customHeight="1" spans="2:2">
+    <row r="4" customHeight="1" spans="2:3">
       <c r="B4"/>
-    </row>
-    <row r="5" customHeight="1" spans="2:2">
+      <c r="C4"/>
+    </row>
+    <row r="5" customHeight="1" spans="2:3">
       <c r="B5"/>
-    </row>
-    <row r="6" customHeight="1" spans="2:2">
+      <c r="C5"/>
+    </row>
+    <row r="6" customHeight="1" spans="2:3">
       <c r="B6"/>
-    </row>
-    <row r="7" customHeight="1" spans="2:2">
+      <c r="C6"/>
+    </row>
+    <row r="7" customHeight="1" spans="2:3">
       <c r="B7"/>
-    </row>
-    <row r="8" customHeight="1" spans="2:2">
+      <c r="C7"/>
+    </row>
+    <row r="8" customHeight="1" spans="2:3">
       <c r="B8"/>
-    </row>
-    <row r="9" customHeight="1" spans="2:2">
+      <c r="C8"/>
+    </row>
+    <row r="9" customHeight="1" spans="2:3">
       <c r="B9"/>
-    </row>
-    <row r="10" customHeight="1" spans="2:2">
+      <c r="C9"/>
+    </row>
+    <row r="10" customHeight="1" spans="2:3">
       <c r="B10"/>
-    </row>
-    <row r="11" customHeight="1" spans="2:3">
+      <c r="C10"/>
+    </row>
+    <row r="11" customHeight="1" spans="2:4">
       <c r="B11"/>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" customHeight="1" spans="2:2">
+      <c r="C11"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" customHeight="1" spans="2:3">
       <c r="B12"/>
-    </row>
-    <row r="13" customHeight="1" spans="2:2">
+      <c r="C12"/>
+    </row>
+    <row r="13" customHeight="1" spans="2:3">
       <c r="B13"/>
-    </row>
-    <row r="14" customHeight="1" spans="2:2">
+      <c r="C13"/>
+    </row>
+    <row r="14" customHeight="1" spans="2:3">
       <c r="B14"/>
-    </row>
-    <row r="15" customHeight="1" spans="2:2">
+      <c r="C14"/>
+    </row>
+    <row r="15" customHeight="1" spans="2:3">
       <c r="B15"/>
-    </row>
-    <row r="16" customHeight="1" spans="2:2">
+      <c r="C15"/>
+    </row>
+    <row r="16" customHeight="1" spans="2:3">
       <c r="B16"/>
-    </row>
-    <row r="17" customHeight="1" spans="2:2">
+      <c r="C16"/>
+    </row>
+    <row r="17" customHeight="1" spans="2:3">
       <c r="B17"/>
-    </row>
-    <row r="18" customHeight="1" spans="2:2">
+      <c r="C17"/>
+    </row>
+    <row r="18" customHeight="1" spans="2:3">
       <c r="B18"/>
-    </row>
-    <row r="19" customHeight="1" spans="2:2">
+      <c r="C18"/>
+    </row>
+    <row r="19" customHeight="1" spans="2:3">
       <c r="B19"/>
-    </row>
-    <row r="20" customHeight="1" spans="2:2">
+      <c r="C19"/>
+    </row>
+    <row r="20" customHeight="1" spans="2:3">
       <c r="B20"/>
-    </row>
-    <row r="21" customHeight="1" spans="2:2">
+      <c r="C20"/>
+    </row>
+    <row r="21" customHeight="1" spans="2:3">
       <c r="B21"/>
-    </row>
-    <row r="22" customHeight="1" spans="2:2">
+      <c r="C21"/>
+    </row>
+    <row r="22" customHeight="1" spans="2:3">
       <c r="B22"/>
-    </row>
-    <row r="23" customHeight="1" spans="2:2">
+      <c r="C22"/>
+    </row>
+    <row r="23" customHeight="1" spans="2:3">
       <c r="B23"/>
-    </row>
-    <row r="24" customHeight="1" spans="2:2">
+      <c r="C23"/>
+    </row>
+    <row r="24" customHeight="1" spans="2:3">
       <c r="B24"/>
-    </row>
-    <row r="25" customHeight="1" spans="2:2">
+      <c r="C24"/>
+    </row>
+    <row r="25" customHeight="1" spans="2:3">
       <c r="B25"/>
-    </row>
-    <row r="26" customHeight="1" spans="2:2">
+      <c r="C25"/>
+    </row>
+    <row r="26" customHeight="1" spans="2:3">
       <c r="B26"/>
-    </row>
-    <row r="27" customHeight="1" spans="2:2">
+      <c r="C26"/>
+    </row>
+    <row r="27" customHeight="1" spans="2:3">
       <c r="B27"/>
-    </row>
-    <row r="28" customHeight="1" spans="2:2">
+      <c r="C27"/>
+    </row>
+    <row r="28" customHeight="1" spans="2:3">
       <c r="B28"/>
-    </row>
-    <row r="29" customHeight="1" spans="2:2">
+      <c r="C28"/>
+    </row>
+    <row r="29" customHeight="1" spans="2:3">
       <c r="B29"/>
-    </row>
-    <row r="30" customHeight="1" spans="2:2">
+      <c r="C29"/>
+    </row>
+    <row r="30" customHeight="1" spans="2:3">
       <c r="B30"/>
-    </row>
-    <row r="31" customHeight="1" spans="2:2">
+      <c r="C30"/>
+    </row>
+    <row r="31" customHeight="1" spans="2:3">
       <c r="B31"/>
-    </row>
-    <row r="32" customHeight="1" spans="2:2">
+      <c r="C31"/>
+    </row>
+    <row r="32" customHeight="1" spans="2:3">
       <c r="B32"/>
-    </row>
-    <row r="33" customHeight="1" spans="2:2">
+      <c r="C32"/>
+    </row>
+    <row r="33" customHeight="1" spans="2:3">
       <c r="B33"/>
-    </row>
-    <row r="34" customHeight="1" spans="2:2">
+      <c r="C33"/>
+    </row>
+    <row r="34" customHeight="1" spans="2:3">
       <c r="B34"/>
-    </row>
-    <row r="35" customHeight="1" spans="2:2">
+      <c r="C34"/>
+    </row>
+    <row r="35" customHeight="1" spans="2:3">
       <c r="B35"/>
-    </row>
-    <row r="36" customHeight="1" spans="2:2">
+      <c r="C35"/>
+    </row>
+    <row r="36" customHeight="1" spans="2:3">
       <c r="B36"/>
-    </row>
-    <row r="37" customHeight="1" spans="2:2">
+      <c r="C36"/>
+    </row>
+    <row r="37" customHeight="1" spans="2:3">
       <c r="B37"/>
-    </row>
-    <row r="38" customHeight="1" spans="2:2">
+      <c r="C37"/>
+    </row>
+    <row r="38" customHeight="1" spans="2:3">
       <c r="B38"/>
-    </row>
-    <row r="39" customHeight="1" spans="2:2">
+      <c r="C38"/>
+    </row>
+    <row r="39" customHeight="1" spans="2:3">
       <c r="B39"/>
-    </row>
-    <row r="40" customHeight="1" spans="2:2">
+      <c r="C39"/>
+    </row>
+    <row r="40" customHeight="1" spans="2:3">
       <c r="B40"/>
-    </row>
-    <row r="41" customHeight="1" spans="2:2">
+      <c r="C40"/>
+    </row>
+    <row r="41" customHeight="1" spans="2:3">
       <c r="B41"/>
-    </row>
-    <row r="42" customHeight="1" spans="2:2">
+      <c r="C41"/>
+    </row>
+    <row r="42" customHeight="1" spans="2:3">
       <c r="B42"/>
-    </row>
-    <row r="43" customHeight="1" spans="2:2">
+      <c r="C42"/>
+    </row>
+    <row r="43" customHeight="1" spans="2:3">
       <c r="B43"/>
-    </row>
-    <row r="44" customHeight="1" spans="2:2">
+      <c r="C43"/>
+    </row>
+    <row r="44" customHeight="1" spans="2:3">
       <c r="B44"/>
-    </row>
-    <row r="45" customHeight="1" spans="2:2">
+      <c r="C44"/>
+    </row>
+    <row r="45" customHeight="1" spans="2:3">
       <c r="B45"/>
-    </row>
-    <row r="46" customHeight="1" spans="2:2">
+      <c r="C45"/>
+    </row>
+    <row r="46" customHeight="1" spans="2:3">
       <c r="B46"/>
-    </row>
-    <row r="47" customHeight="1" spans="2:2">
+      <c r="C46"/>
+    </row>
+    <row r="47" customHeight="1" spans="2:3">
       <c r="B47"/>
-    </row>
-    <row r="48" customHeight="1" spans="2:2">
+      <c r="C47"/>
+    </row>
+    <row r="48" customHeight="1" spans="2:3">
       <c r="B48"/>
-    </row>
-    <row r="49" customHeight="1" spans="2:2">
+      <c r="C48"/>
+    </row>
+    <row r="49" customHeight="1" spans="2:3">
       <c r="B49"/>
-    </row>
-    <row r="50" customHeight="1" spans="2:2">
+      <c r="C49"/>
+    </row>
+    <row r="50" customHeight="1" spans="2:3">
       <c r="B50"/>
-    </row>
-    <row r="51" customHeight="1" spans="2:2">
+      <c r="C50"/>
+    </row>
+    <row r="51" customHeight="1" spans="2:3">
       <c r="B51"/>
-    </row>
-    <row r="52" customHeight="1" spans="2:2">
+      <c r="C51"/>
+    </row>
+    <row r="52" customHeight="1" spans="2:3">
       <c r="B52"/>
-    </row>
-    <row r="53" customHeight="1" spans="2:2">
+      <c r="C52"/>
+    </row>
+    <row r="53" customHeight="1" spans="2:3">
       <c r="B53"/>
-    </row>
-    <row r="54" customHeight="1" spans="2:2">
+      <c r="C53"/>
+    </row>
+    <row r="54" customHeight="1" spans="2:3">
       <c r="B54"/>
-    </row>
-    <row r="55" customHeight="1" spans="2:2">
+      <c r="C54"/>
+    </row>
+    <row r="55" customHeight="1" spans="2:3">
       <c r="B55"/>
-    </row>
-    <row r="56" customHeight="1" spans="2:2">
+      <c r="C55"/>
+    </row>
+    <row r="56" customHeight="1" spans="2:3">
       <c r="B56"/>
-    </row>
-    <row r="57" customHeight="1" spans="2:2">
+      <c r="C56"/>
+    </row>
+    <row r="57" customHeight="1" spans="2:3">
       <c r="B57"/>
-    </row>
-    <row r="58" customHeight="1" spans="2:2">
+      <c r="C57"/>
+    </row>
+    <row r="58" customHeight="1" spans="2:3">
       <c r="B58"/>
-    </row>
-    <row r="59" customHeight="1" spans="2:2">
+      <c r="C58"/>
+    </row>
+    <row r="59" customHeight="1" spans="2:3">
       <c r="B59"/>
-    </row>
-    <row r="60" customHeight="1" spans="2:2">
+      <c r="C59"/>
+    </row>
+    <row r="60" customHeight="1" spans="2:3">
       <c r="B60"/>
-    </row>
-    <row r="61" customHeight="1" spans="2:2">
+      <c r="C60"/>
+    </row>
+    <row r="61" customHeight="1" spans="2:3">
       <c r="B61"/>
-    </row>
-    <row r="62" customHeight="1" spans="2:2">
+      <c r="C61"/>
+    </row>
+    <row r="62" customHeight="1" spans="2:3">
       <c r="B62"/>
-    </row>
-    <row r="63" customHeight="1" spans="2:2">
+      <c r="C62"/>
+    </row>
+    <row r="63" customHeight="1" spans="2:3">
       <c r="B63"/>
-    </row>
-    <row r="64" customHeight="1" spans="2:2">
+      <c r="C63"/>
+    </row>
+    <row r="64" customHeight="1" spans="2:3">
       <c r="B64"/>
-    </row>
-    <row r="65" customHeight="1" spans="2:2">
+      <c r="C64"/>
+    </row>
+    <row r="65" customHeight="1" spans="2:3">
       <c r="B65"/>
-    </row>
-    <row r="66" customHeight="1" spans="2:2">
+      <c r="C65"/>
+    </row>
+    <row r="66" customHeight="1" spans="2:3">
       <c r="B66"/>
-    </row>
-    <row r="67" customHeight="1" spans="2:2">
+      <c r="C66"/>
+    </row>
+    <row r="67" customHeight="1" spans="2:3">
       <c r="B67"/>
-    </row>
-    <row r="68" customHeight="1" spans="2:2">
+      <c r="C67"/>
+    </row>
+    <row r="68" customHeight="1" spans="2:3">
       <c r="B68"/>
-    </row>
-    <row r="69" customHeight="1" spans="2:2">
+      <c r="C68"/>
+    </row>
+    <row r="69" customHeight="1" spans="2:3">
       <c r="B69"/>
-    </row>
-    <row r="70" customHeight="1" spans="2:2">
+      <c r="C69"/>
+    </row>
+    <row r="70" customHeight="1" spans="2:3">
       <c r="B70"/>
-    </row>
-    <row r="71" customHeight="1" spans="2:2">
+      <c r="C70"/>
+    </row>
+    <row r="71" customHeight="1" spans="2:3">
       <c r="B71"/>
-    </row>
-    <row r="72" customHeight="1" spans="2:2">
+      <c r="C71"/>
+    </row>
+    <row r="72" customHeight="1" spans="2:3">
       <c r="B72"/>
-    </row>
-    <row r="73" customHeight="1" spans="2:2">
+      <c r="C72"/>
+    </row>
+    <row r="73" customHeight="1" spans="2:3">
       <c r="B73"/>
-    </row>
-    <row r="74" customHeight="1" spans="2:2">
+      <c r="C73"/>
+    </row>
+    <row r="74" customHeight="1" spans="2:3">
       <c r="B74"/>
-    </row>
-    <row r="75" customHeight="1" spans="2:2">
+      <c r="C74"/>
+    </row>
+    <row r="75" customHeight="1" spans="2:3">
       <c r="B75"/>
-    </row>
-    <row r="76" customHeight="1" spans="2:2">
+      <c r="C75"/>
+    </row>
+    <row r="76" customHeight="1" spans="2:3">
       <c r="B76"/>
-    </row>
-    <row r="77" customHeight="1" spans="2:2">
+      <c r="C76"/>
+    </row>
+    <row r="77" customHeight="1" spans="2:3">
       <c r="B77"/>
-    </row>
-    <row r="78" customHeight="1" spans="2:2">
+      <c r="C77"/>
+    </row>
+    <row r="78" customHeight="1" spans="2:3">
       <c r="B78"/>
-    </row>
-    <row r="79" customHeight="1" spans="2:2">
+      <c r="C78"/>
+    </row>
+    <row r="79" customHeight="1" spans="2:3">
       <c r="B79"/>
-    </row>
-    <row r="80" customHeight="1" spans="2:2">
+      <c r="C79"/>
+    </row>
+    <row r="80" customHeight="1" spans="2:3">
       <c r="B80"/>
-    </row>
-    <row r="81" customHeight="1" spans="2:2">
+      <c r="C80"/>
+    </row>
+    <row r="81" customHeight="1" spans="2:3">
       <c r="B81"/>
-    </row>
-    <row r="82" customHeight="1" spans="2:2">
+      <c r="C81"/>
+    </row>
+    <row r="82" customHeight="1" spans="2:3">
       <c r="B82"/>
-    </row>
-    <row r="83" customHeight="1" spans="2:2">
+      <c r="C82"/>
+    </row>
+    <row r="83" customHeight="1" spans="2:3">
       <c r="B83"/>
-    </row>
-    <row r="84" customHeight="1" spans="2:2">
+      <c r="C83"/>
+    </row>
+    <row r="84" customHeight="1" spans="2:3">
       <c r="B84"/>
-    </row>
-    <row r="85" customHeight="1" spans="2:2">
+      <c r="C84"/>
+    </row>
+    <row r="85" customHeight="1" spans="2:3">
       <c r="B85"/>
-    </row>
-    <row r="86" customHeight="1" spans="2:2">
+      <c r="C85"/>
+    </row>
+    <row r="86" customHeight="1" spans="2:3">
       <c r="B86"/>
-    </row>
-    <row r="87" customHeight="1" spans="2:2">
+      <c r="C86"/>
+    </row>
+    <row r="87" customHeight="1" spans="2:3">
       <c r="B87"/>
-    </row>
-    <row r="88" customHeight="1" spans="2:2">
+      <c r="C87"/>
+    </row>
+    <row r="88" customHeight="1" spans="2:3">
       <c r="B88"/>
-    </row>
-    <row r="89" customHeight="1" spans="2:2">
+      <c r="C88"/>
+    </row>
+    <row r="89" customHeight="1" spans="2:3">
       <c r="B89"/>
-    </row>
-    <row r="90" customHeight="1" spans="2:2">
+      <c r="C89"/>
+    </row>
+    <row r="90" customHeight="1" spans="2:3">
       <c r="B90"/>
-    </row>
-    <row r="91" customHeight="1" spans="2:2">
+      <c r="C90"/>
+    </row>
+    <row r="91" customHeight="1" spans="2:3">
       <c r="B91"/>
-    </row>
-    <row r="92" customHeight="1" spans="2:2">
+      <c r="C91"/>
+    </row>
+    <row r="92" customHeight="1" spans="2:3">
       <c r="B92"/>
-    </row>
-    <row r="93" customHeight="1" spans="2:2">
+      <c r="C92"/>
+    </row>
+    <row r="93" customHeight="1" spans="2:3">
       <c r="B93"/>
-    </row>
-    <row r="94" customHeight="1" spans="2:2">
+      <c r="C93"/>
+    </row>
+    <row r="94" customHeight="1" spans="2:3">
       <c r="B94"/>
-    </row>
-    <row r="95" customHeight="1" spans="2:2">
+      <c r="C94"/>
+    </row>
+    <row r="95" customHeight="1" spans="2:3">
       <c r="B95"/>
-    </row>
-    <row r="96" customHeight="1" spans="2:2">
+      <c r="C95"/>
+    </row>
+    <row r="96" customHeight="1" spans="2:3">
       <c r="B96"/>
-    </row>
-    <row r="97" customHeight="1" spans="2:2">
+      <c r="C96"/>
+    </row>
+    <row r="97" customHeight="1" spans="2:3">
       <c r="B97"/>
-    </row>
-    <row r="98" customHeight="1" spans="2:2">
+      <c r="C97"/>
+    </row>
+    <row r="98" customHeight="1" spans="2:3">
       <c r="B98"/>
-    </row>
-    <row r="99" customHeight="1" spans="2:2">
+      <c r="C98"/>
+    </row>
+    <row r="99" customHeight="1" spans="2:3">
       <c r="B99"/>
-    </row>
-    <row r="100" customHeight="1" spans="2:2">
+      <c r="C99"/>
+    </row>
+    <row r="100" customHeight="1" spans="2:3">
       <c r="B100"/>
-    </row>
-    <row r="101" customHeight="1" spans="2:2">
+      <c r="C100"/>
+    </row>
+    <row r="101" customHeight="1" spans="2:3">
       <c r="B101"/>
-    </row>
-    <row r="102" customHeight="1" spans="2:2">
+      <c r="C101"/>
+    </row>
+    <row r="102" customHeight="1" spans="2:3">
       <c r="B102"/>
-    </row>
-    <row r="103" customHeight="1" spans="2:2">
+      <c r="C102"/>
+    </row>
+    <row r="103" customHeight="1" spans="2:3">
       <c r="B103"/>
-    </row>
-    <row r="104" customHeight="1" spans="2:2">
+      <c r="C103"/>
+    </row>
+    <row r="104" customHeight="1" spans="2:3">
       <c r="B104"/>
-    </row>
-    <row r="105" customHeight="1" spans="2:2">
+      <c r="C104"/>
+    </row>
+    <row r="105" customHeight="1" spans="2:3">
       <c r="B105"/>
-    </row>
-    <row r="106" customHeight="1" spans="2:2">
+      <c r="C105"/>
+    </row>
+    <row r="106" customHeight="1" spans="2:3">
       <c r="B106"/>
-    </row>
-    <row r="107" customHeight="1" spans="2:2">
+      <c r="C106"/>
+    </row>
+    <row r="107" customHeight="1" spans="2:3">
       <c r="B107"/>
-    </row>
-    <row r="108" customHeight="1" spans="2:2">
+      <c r="C107"/>
+    </row>
+    <row r="108" customHeight="1" spans="2:3">
       <c r="B108"/>
-    </row>
-    <row r="109" customHeight="1" spans="2:2">
+      <c r="C108"/>
+    </row>
+    <row r="109" customHeight="1" spans="2:3">
       <c r="B109"/>
-    </row>
-    <row r="110" customHeight="1" spans="2:2">
+      <c r="C109"/>
+    </row>
+    <row r="110" customHeight="1" spans="2:3">
       <c r="B110"/>
-    </row>
-    <row r="111" customHeight="1" spans="2:2">
+      <c r="C110"/>
+    </row>
+    <row r="111" customHeight="1" spans="2:3">
       <c r="B111"/>
-    </row>
-    <row r="112" customHeight="1" spans="2:2">
+      <c r="C111"/>
+    </row>
+    <row r="112" customHeight="1" spans="2:3">
       <c r="B112"/>
-    </row>
-    <row r="113" customHeight="1" spans="2:2">
+      <c r="C112"/>
+    </row>
+    <row r="113" customHeight="1" spans="2:3">
       <c r="B113"/>
-    </row>
-    <row r="114" customHeight="1" spans="2:2">
+      <c r="C113"/>
+    </row>
+    <row r="114" customHeight="1" spans="2:3">
       <c r="B114"/>
-    </row>
-    <row r="115" customHeight="1" spans="2:2">
+      <c r="C114"/>
+    </row>
+    <row r="115" customHeight="1" spans="2:3">
       <c r="B115"/>
-    </row>
-    <row r="116" customHeight="1" spans="2:2">
+      <c r="C115"/>
+    </row>
+    <row r="116" customHeight="1" spans="2:3">
       <c r="B116"/>
-    </row>
-    <row r="117" customHeight="1" spans="2:2">
+      <c r="C116"/>
+    </row>
+    <row r="117" customHeight="1" spans="2:3">
       <c r="B117"/>
-    </row>
-    <row r="118" customHeight="1" spans="2:2">
+      <c r="C117"/>
+    </row>
+    <row r="118" customHeight="1" spans="2:3">
       <c r="B118"/>
-    </row>
-    <row r="119" customHeight="1" spans="2:2">
+      <c r="C118"/>
+    </row>
+    <row r="119" customHeight="1" spans="2:3">
       <c r="B119"/>
-    </row>
-    <row r="120" customHeight="1" spans="2:2">
+      <c r="C119"/>
+    </row>
+    <row r="120" customHeight="1" spans="2:3">
       <c r="B120"/>
-    </row>
-    <row r="121" customHeight="1" spans="2:2">
+      <c r="C120"/>
+    </row>
+    <row r="121" customHeight="1" spans="2:3">
       <c r="B121"/>
-    </row>
-    <row r="122" customHeight="1" spans="2:2">
+      <c r="C121"/>
+    </row>
+    <row r="122" customHeight="1" spans="2:3">
       <c r="B122"/>
-    </row>
-    <row r="123" customHeight="1" spans="2:2">
+      <c r="C122"/>
+    </row>
+    <row r="123" customHeight="1" spans="2:3">
       <c r="B123"/>
+      <c r="C123"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="53.9090909090909" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="71" customHeight="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/public/static/销售订单导入模板.xlsx
+++ b/public/static/销售订单导入模板.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>序号</t>
   </si>
@@ -72,7 +72,10 @@
     <t>包装方式</t>
   </si>
   <si>
-    <t>1、客户货号和规格型号必须填写一项</t>
+    <t>特殊要求</t>
+  </si>
+  <si>
+    <t>1、客户料号和品名规格必须填写其中一项</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1094,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N123"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.63636363636364" style="2" customWidth="1"/>
@@ -1105,10 +1108,10 @@
     <col min="9" max="9" width="10.5454545454545" style="2" customWidth="1"/>
     <col min="10" max="10" width="10" style="2" customWidth="1"/>
     <col min="11" max="13" width="11.6363636363636" style="2" customWidth="1"/>
-    <col min="14" max="14" width="12.0909090909091" style="2" customWidth="1"/>
+    <col min="14" max="15" width="12.0909090909091" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1151,8 +1154,11 @@
       <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:14">
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:15">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1167,6 +1173,7 @@
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
     </row>
     <row r="3" customFormat="1" customHeight="1"/>
     <row r="4" customHeight="1" spans="2:3">
@@ -1667,7 +1674,7 @@
   <sheetData>
     <row r="1" ht="71" customHeight="1" spans="1:1">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
